--- a/public/templates/forms/A-003-MasterAssetInventory-FORM.xlsx
+++ b/public/templates/forms/A-003-MasterAssetInventory-FORM.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="0"/>
   <fonts count="11">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -309,7 +309,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -343,7 +343,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>

--- a/public/templates/forms/A-003-MasterAssetInventory-FORM.xlsx
+++ b/public/templates/forms/A-003-MasterAssetInventory-FORM.xlsx
@@ -4,20 +4,25 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Register!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -135,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -188,6 +193,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -553,7 +561,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -756,7 +764,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>AST-001</t>
@@ -982,7 +990,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
+    <row r="26" ht="34.7" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
           <t>AST-001</t>
@@ -1098,7 +1106,6 @@
       </c>
       <c r="C36" s="11">
         <f>COUNTA(A12:A21)</f>
-        <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
@@ -1109,7 +1116,6 @@
       </c>
       <c r="C37" s="11">
         <f>COUNTIF(I12:I21,"Active")</f>
-        <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
@@ -1120,7 +1126,6 @@
       </c>
       <c r="C38" s="11">
         <f>COUNTIF(I12:I21,"Under Review")</f>
-        <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
@@ -1131,7 +1136,6 @@
       </c>
       <c r="C39" s="11">
         <f>COUNTIF(I12:I21,"Retired")</f>
-        <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
@@ -1142,7 +1146,6 @@
       </c>
       <c r="C40" s="11">
         <f>COUNTIF(I12:I21,"Decommissioned")</f>
-        <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
@@ -1153,7 +1156,6 @@
       </c>
       <c r="C41" s="11">
         <f>COUNTIF(K12:K21,"&lt;"&amp;TODAY())</f>
-        <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1"/>
@@ -1230,7 +1232,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="19.5" customHeight="1">
+    <row r="53" ht="50.5" customHeight="1">
       <c r="A53" s="9" t="inlineStr">
         <is>
           <t>[Approving official / title]</t>
@@ -1240,7 +1242,7 @@
       <c r="C53" s="9" t="n"/>
       <c r="D53" s="9" t="n"/>
     </row>
-    <row r="54" ht="19.5" customHeight="1">
+    <row r="54" ht="34.7" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
           <t>[Owner role]</t>
@@ -1338,7 +1340,8 @@
     <mergeCell ref="A44:K44"/>
     <mergeCell ref="A9:K9"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1346,7 +1349,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1371,7 +1374,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, summary, downstream use, source authority, signatures and revision history live on the Register tab.</t>
@@ -1408,7 +1411,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
           <t>ID</t>
@@ -1518,7 +1521,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Owner (Role)</t>
@@ -1584,7 +1587,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
+    <row r="15" ht="34.7" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Status</t>
@@ -1622,13 +1625,11 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
+      <c r="D16" s="20">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="17" ht="34.7" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Next Review Due</t>
@@ -1644,10 +1645,8 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
+      <c r="D17" s="20">
+        <v>46174</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1725,6 +1724,7 @@
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B24:D24"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>